--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE DE LUZ 03_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CHAVE DE LUZ 03_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,11 +472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -528,11 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +528,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,11 +548,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -599,7 +568,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -620,7 +588,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -641,11 +608,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -666,7 +628,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -687,11 +648,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -712,11 +668,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -737,7 +688,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -754,11 +704,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -779,7 +724,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -800,7 +744,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -821,7 +764,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -842,7 +784,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -863,7 +804,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -876,7 +816,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CHAVE LUZ  LADO ESQUERDO CONDOR CTZ CROSSER150 2015 A 2016</t>
+          <t>CHAVE LUZ  LADO ESQUERDO CONDOR XTZ CROSSER150 2015 A 2016</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -884,7 +824,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -905,7 +844,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -926,7 +864,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -947,7 +884,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -968,7 +904,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -989,7 +924,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1010,7 +944,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1031,7 +964,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1052,7 +984,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1073,7 +1004,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1094,7 +1024,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1115,7 +1044,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1124,7 +1052,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PUNHO LUZ CB250 TWISTER</t>
+          <t>PUNHO LUZ RT CB250 TWISTER</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1132,7 +1060,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1150,10 +1077,9 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1171,10 +1097,9 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1193,11 +1118,6 @@
       <c r="D36" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
     </row>
